--- a/data/dividends_info_20261011.xlsx
+++ b/data/dividends_info_20261011.xlsx
@@ -1580,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1688,7 +1688,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1800,14 +1800,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1817,14 +1817,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1834,14 +1834,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1868,14 +1868,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1892,7 +1892,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1902,14 +1902,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1919,14 +1919,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1943,46 +1943,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1994,12 +1994,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2028,63 +2028,63 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2096,97 +2096,97 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2198,97 +2198,97 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2300,12 +2300,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2317,29 +2317,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2351,63 +2351,63 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2419,29 +2419,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2453,58 +2453,58 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2538,46 +2538,46 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2589,29 +2589,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2623,29 +2623,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2657,97 +2657,97 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2759,12 +2759,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2776,29 +2776,29 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2810,29 +2810,29 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2844,12 +2844,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2861,63 +2861,63 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2929,29 +2929,29 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2963,12 +2963,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2980,12 +2980,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3014,12 +3014,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3031,29 +3031,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3065,46 +3065,46 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3116,29 +3116,29 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3150,29 +3150,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3184,12 +3184,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3201,29 +3201,29 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3235,29 +3235,29 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3269,46 +3269,46 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3320,12 +3320,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3337,12 +3337,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3354,12 +3354,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3371,29 +3371,29 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3405,12 +3405,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3456,7 +3456,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3473,7 +3473,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3483,14 +3483,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3507,7 +3507,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3517,14 +3517,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3541,7 +3541,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3568,14 +3568,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3585,19 +3585,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3609,29 +3609,29 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3643,12 +3643,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3660,12 +3660,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3677,12 +3677,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3694,29 +3694,29 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3728,29 +3728,29 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3762,12 +3762,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3779,12 +3779,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3796,29 +3796,29 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3830,12 +3830,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3847,46 +3847,46 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3898,12 +3898,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3932,46 +3932,46 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3983,29 +3983,29 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4017,12 +4017,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4034,29 +4034,29 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4068,12 +4068,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4085,12 +4085,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4102,29 +4102,29 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4136,15 +4136,355 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>Pharmanutra S.p.A.</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>VALSOIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>doValue S.p.A.</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Neodecortech S.p.A.</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>RECORDATI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>SABAF S.p.A.</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SABAF S.p.A.</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>RISANAMENTO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>RISANAMENTO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SAFILO GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>RISANAMENTO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>BFF Bank S.P.A.</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>INWIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>FOPE S.p.A.</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Banca Generali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>A2A S.p.A.</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TELECOM ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Industrie De Nora S.p.A.</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>VALTECNE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
         </is>
@@ -4174,316 +4514,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A2A S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BFF Bank S.P.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SABAF S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SABAF S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SAFILO GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>VALTECNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>